--- a/resultados/Resultados_FacebookAI_xlm-roberta-large.xlsx
+++ b/resultados/Resultados_FacebookAI_xlm-roberta-large.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UMA\TFG\TFG-Sistema-Recomendacion-Personalidad\resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5207A826-F21A-4BAF-A449-53BC5F1B7906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9997D8-8F23-4DE3-8D06-4894459B1DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMOTE" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="308">
   <si>
     <t>Modelos</t>
   </si>
@@ -47,887 +47,843 @@
     <t>Matriz Confusion</t>
   </si>
   <si>
-    <t>Regresión Logística E/I</t>
-  </si>
-  <si>
-    <t>Regresión Logística S/N</t>
+    <t>0: 200
+1: 668</t>
+  </si>
+  <si>
+    <t>0: 0.31
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 120
+1: 748</t>
+  </si>
+  <si>
+    <t>Parametros</t>
+  </si>
+  <si>
+    <t>{'penalty': None, 'C': 9.732719859279047, 'solver': 'lbfgs', 'tol': 0.00010564097578389837, 'class_weight': 'balanced', 'random_state': 42, 'n_jobs': -1, 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>0: 0.71
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 398
+1: 470</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.62
+1: 0.67</t>
+  </si>
+  <si>
+    <t>0: 344
+1: 524</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.22
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.91</t>
+  </si>
+  <si>
+    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[105 95]
+ [92 576]]</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.95</t>
+  </si>
+  <si>
+    <t>0: 0.77
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[92 28]
+ [251 497]]</t>
+  </si>
+  <si>
+    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.95</t>
+  </si>
+  <si>
+    <t>0: 0.98
+1: 0.41</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.57</t>
+  </si>
+  <si>
+    <t>[[389 9]
+ [279 191]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.89
+1: 0.31</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.44</t>
+  </si>
+  <si>
+    <t>[[307 37]
+ [364 160]]</t>
+  </si>
+  <si>
+    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.80</t>
+  </si>
+  <si>
+    <t>0: 0.78
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.76
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[310 88]
+ [112 358]]</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.75</t>
+  </si>
+  <si>
+    <t>[[130 214]
+ [81 443]]</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.85</t>
+  </si>
+  <si>
+    <t>0: 0.84
+1: 0.27</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.41</t>
+  </si>
+  <si>
+    <t>[[168 32]
+ [488 180]]</t>
+  </si>
+  <si>
+    <t>0: 0.15
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.74
+1: 0.31</t>
+  </si>
+  <si>
+    <t>0: 0.25
+1: 0.46</t>
+  </si>
+  <si>
+    <t>[[89 31]
+ [514 234]]</t>
+  </si>
+  <si>
+    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.67</t>
+  </si>
+  <si>
+    <t>[[230 168]
+ [145 325]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.63</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.65</t>
+  </si>
+  <si>
+    <t>[[143 201]
+ [177 347]]</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.16
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.38
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.23
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[46 74]
+ [233 515]]</t>
+  </si>
+  <si>
+    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
+  </si>
+  <si>
+    <t>0: 0.60
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.63</t>
+  </si>
+  <si>
+    <t>0: 0.63
+1: 0.66</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.62</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.65</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.64</t>
+  </si>
+  <si>
+    <t>[[136 208]
+ [182 342]]</t>
+  </si>
+  <si>
+    <t>LR E/I</t>
+  </si>
+  <si>
+    <t>0: 0.47
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.83</t>
+  </si>
+  <si>
+    <t>[[133 67]
+ [151 517]]</t>
+  </si>
+  <si>
+    <t>LR S/N</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[71 49]
+ [156 592]]</t>
+  </si>
+  <si>
+    <t>LR T/F</t>
+  </si>
+  <si>
+    <t>[[306 92]
+ [126 344]]</t>
+  </si>
+  <si>
+    <t>LR J/P</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.67</t>
+  </si>
+  <si>
+    <t>0: 0.58
+1: 0.70</t>
+  </si>
+  <si>
+    <t>[[211 133]
+ [171 353]]</t>
+  </si>
+  <si>
+    <t>XGB E/I</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[66 134]
+ [76 592]]</t>
+  </si>
+  <si>
+    <t>XGB S/N</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.25
+1: 0.94</t>
+  </si>
+  <si>
+    <t>0: 0.31
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[30 90]
+ [42 706]]</t>
+  </si>
+  <si>
+    <t>XGB T/F</t>
+  </si>
+  <si>
+    <t>0: 0.73
+1: 0.79</t>
+  </si>
+  <si>
+    <t>0: 0.76
+1: 0.77</t>
+  </si>
+  <si>
+    <t>0: 0.75
+1: 0.78</t>
+  </si>
+  <si>
+    <t>[[302 96]
+ [109 361]]</t>
+  </si>
+  <si>
+    <t>XGB J/P</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.65</t>
+  </si>
+  <si>
+    <t>0: 0.31
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.73</t>
+  </si>
+  <si>
+    <t>[[108 236]
+ [83 441]]</t>
+  </si>
+  <si>
+    <t>LSVC E/I</t>
+  </si>
+  <si>
+    <t>LSVC S/N</t>
+  </si>
+  <si>
+    <t>LSVC T/F</t>
+  </si>
+  <si>
+    <t>LSVC J/P</t>
+  </si>
+  <si>
+    <t>MLPC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[133 67]
+ [183 485]]</t>
+  </si>
+  <si>
+    <t>MLPC S/N</t>
+  </si>
+  <si>
+    <t>0: 0.39
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.90</t>
+  </si>
+  <si>
+    <t>[[52 68]
+ [82 666]]</t>
+  </si>
+  <si>
+    <t>MLPC T/F</t>
+  </si>
+  <si>
+    <t>MLPC J/P</t>
+  </si>
+  <si>
+    <t>KNC E/I</t>
+  </si>
+  <si>
+    <t>KNC S/N</t>
+  </si>
+  <si>
+    <t>KNC T/F</t>
+  </si>
+  <si>
+    <t>KNC J/P</t>
+  </si>
+  <si>
+    <t>DTC E/I</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.65</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.72</t>
+  </si>
+  <si>
+    <t>[[98 102]
+ [237 431]]</t>
+  </si>
+  <si>
+    <t>DTC S/N</t>
+  </si>
+  <si>
+    <t>DTC T/F</t>
+  </si>
+  <si>
+    <t>[[266 132]
+ [174 296]]</t>
+  </si>
+  <si>
+    <t>DTC J/P</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.29
+1: 0.91</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.86
+1: 0.53</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.68</t>
+  </si>
+  <si>
+    <t>[[173 27]
+ [312 356]]</t>
+  </si>
+  <si>
+    <t>0: 0.64
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.12
+1: 0.99</t>
+  </si>
+  <si>
+    <t>0: 0.20
+1: 0.93</t>
+  </si>
+  <si>
+    <t>[[14 106]
+ [8 740]]</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.64
+1: 0.73</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[127 73]
+ [179 489]]</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.86</t>
+  </si>
+  <si>
+    <t>0: 0.85
+1: 0.26</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.40</t>
+  </si>
+  <si>
+    <t>[[171 29]
+ [493 175]]</t>
+  </si>
+  <si>
+    <t>0: 0.72
+1: 0.32</t>
+  </si>
+  <si>
+    <t>0: 0.24
+1: 0.47</t>
+  </si>
+  <si>
+    <t>[[87 33]
+ [509 239]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.81</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.70</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.75</t>
+  </si>
+  <si>
+    <t>[[87 113]
+ [201 467]]</t>
+  </si>
+  <si>
+    <t>0: 0.19
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.27
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[51 69]
+ [213 535]]</t>
+  </si>
+  <si>
+    <t>0: 0.44
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.65
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[129 71]
+ [161 507]]</t>
+  </si>
+  <si>
+    <t>0: 0.53
+1: 0.80</t>
+  </si>
+  <si>
+    <t>[[64 56]
+ [153 595]]</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[74 126]
+ [79 589]]</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.23
+1: 0.95</t>
+  </si>
+  <si>
+    <t>[[27 93]
+ [41 707]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.84</t>
+  </si>
+  <si>
+    <t>0: 0.35
+1: 0.87</t>
+  </si>
+  <si>
+    <t>[[50 70]
+ [119 629]]</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.89</t>
+  </si>
+  <si>
+    <t>0: 0.31
+1: 0.93</t>
+  </si>
+  <si>
+    <t>0: 0.35
+1: 0.91</t>
+  </si>
+  <si>
+    <t>[[37 83]
+ [54 694]]</t>
+  </si>
+  <si>
+    <t>0: 0.41
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.67
+1: 0.71</t>
+  </si>
+  <si>
+    <t>0: 0.51
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[133 67]
+ [191 477]]</t>
+  </si>
+  <si>
+    <t>0: 0.88
+1: 0.24</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.38</t>
+  </si>
+  <si>
+    <t>[[175 25]
+ [508 160]]</t>
+  </si>
+  <si>
+    <t>0: 0.14
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.76
+1: 0.28</t>
+  </si>
+  <si>
+    <t>0: 0.24
+1: 0.42</t>
+  </si>
+  <si>
+    <t>[[91 29]
+ [542 206]]</t>
+  </si>
+  <si>
+    <t>0: 0.49
+1: 0.63</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.71</t>
+  </si>
+  <si>
+    <t>[[98 102]
+ [245 423]]</t>
+  </si>
+  <si>
+    <t>0: 0.15
+1: 0.87</t>
+  </si>
+  <si>
+    <t>0: 0.33
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.21
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[40 80]
+ [229 519]]</t>
+  </si>
+  <si>
+    <t>[[129 71]
+ [162 506]]</t>
+  </si>
+  <si>
+    <t>0: 0.30
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.59
+1: 0.78</t>
+  </si>
+  <si>
+    <t>0: 0.40
+1: 0.84</t>
+  </si>
+  <si>
+    <t>[[71 49]
+ [167 581]]</t>
+  </si>
+  <si>
+    <t>0: 0.45
+1: 0.82</t>
+  </si>
+  <si>
+    <t>0: 0.34
+1: 0.88</t>
+  </si>
+  <si>
+    <t>[[68 132]
+ [82 586]]</t>
+  </si>
+  <si>
+    <t>[[26 94]
+ [47 701]]</t>
+  </si>
+  <si>
+    <t>0: 0.96
+1: 0.22</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.36</t>
+  </si>
+  <si>
+    <t>[[193 7]
+ [522 146]]</t>
+  </si>
+  <si>
+    <t>0: 0.32
+1: 0.90</t>
+  </si>
+  <si>
+    <t>0: 0.43
+1: 0.85</t>
+  </si>
+  <si>
+    <t>[[52 68]
+ [110 638]]</t>
+  </si>
+  <si>
+    <t>0: 0.46
+1: 0.86</t>
   </si>
   <si>
     <t>0: 0.58
 1: 0.80</t>
   </si>
   <si>
-    <t>0: 0.41
-1: 0.85</t>
-  </si>
-  <si>
-    <t>Parametros</t>
-  </si>
-  <si>
-    <t>Regresión Logística T/F</t>
-  </si>
-  <si>
-    <t>Regresión Logística J/P</t>
-  </si>
-  <si>
-    <t>XGBoost E/I</t>
-  </si>
-  <si>
-    <t>XGBoost S/N</t>
-  </si>
-  <si>
-    <t>XGBoost T/F</t>
-  </si>
-  <si>
-    <t>XGBoost J/P</t>
-  </si>
-  <si>
-    <t>LinearSVM E/I</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.80</t>
-  </si>
-  <si>
-    <t>LinearSVM S/N</t>
-  </si>
-  <si>
-    <t>0: 0.41
-1: 0.86</t>
-  </si>
-  <si>
-    <t>LinearSVM T/F</t>
-  </si>
-  <si>
-    <t>LinearSVM J/P</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.69</t>
-  </si>
-  <si>
-    <t>MLP E/I</t>
-  </si>
-  <si>
-    <t>MLP S/N</t>
-  </si>
-  <si>
-    <t>MLP T/F</t>
-  </si>
-  <si>
-    <t>MLP J/P</t>
-  </si>
-  <si>
-    <t>{'penalty': None, 'C': 9.732719859279047, 'solver': 'lbfgs', 'tol': 0.00010564097578389837, 'class_weight': 'balanced', 'random_state': 42, 'n_jobs': -1, 'max_iter': 5000}</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.66
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 200
-1: 668</t>
-  </si>
-  <si>
-    <t>[[131 69]
- [160 508]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 120
-1: 748</t>
-  </si>
-  <si>
-    <t>[[64 56]
- [154 594]]</t>
-  </si>
-  <si>
-    <t>0: 0.71
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.77
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 398
-1: 470</t>
-  </si>
-  <si>
-    <t>[[308 90]
- [127 343]]</t>
-  </si>
-  <si>
-    <t>0: 0.55
-1: 0.73</t>
-  </si>
-  <si>
-    <t>0: 0.62
-1: 0.67</t>
-  </si>
-  <si>
-    <t>0: 0.59
-1: 0.70</t>
-  </si>
-  <si>
-    <t>0: 344
-1: 524</t>
-  </si>
-  <si>
-    <t>[[214 130]
- [173 351]]</t>
-  </si>
-  <si>
-    <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.041694500859353036, 'subsample': 0.6688508428769014, 'colsample_bytree': 0.6246885857257476, 'gamma': 0.6844100651211652, 'tree_method': 'hist', 'device': 'cuda', 'random_state': 42, 'n_jobs': 1}</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.85</t>
-  </si>
-  <si>
-    <t>[[71 129]
- [82 586]]</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.22
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[26 94]
- [45 703]]</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.78</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.77</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[293 105]
- [107 363]]</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.33
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.74</t>
-  </si>
-  <si>
-    <t>[[114 230]
- [77 447]]</t>
-  </si>
-  <si>
-    <t>{'loss': 'squared_hinge', 'C': 9.605448156429867, 'tol': 0.0004119653918147926, 'fit_intercept': False, 'random_state': 42, 'class_weight': 'balanced', 'max_iter': 5000}</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.86
-1: 0.53</t>
-  </si>
-  <si>
-    <t>0: 0.51
-1: 0.68</t>
-  </si>
-  <si>
-    <t>[[173 27]
- [312 356]]</t>
-  </si>
-  <si>
-    <t>0: 0.64
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.12
-1: 0.99</t>
-  </si>
-  <si>
-    <t>0: 0.20
-1: 0.93</t>
-  </si>
-  <si>
-    <t>[[14 106]
- [8 740]]</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.95</t>
-  </si>
-  <si>
-    <t>0: 0.98
-1: 0.41</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.57</t>
-  </si>
-  <si>
-    <t>[[389 9]
- [279 191]]</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.89
-1: 0.31</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.44</t>
-  </si>
-  <si>
-    <t>[[307 37]
- [364 160]]</t>
-  </si>
-  <si>
-    <t>{'hidden_layer_sizes': (256, 128, 64), 'activation': 'tanh', 'solver': 'adam', 'learning_rate': 'constant', 'learning_rate_init': 0.001, 'early_stopping': True, 'max_iter': 6000, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.64
-1: 0.73</t>
-  </si>
-  <si>
-    <t>[[127 73]
- [179 489]]</t>
-  </si>
-  <si>
-    <t>0: 0.31
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.88</t>
-  </si>
-  <si>
-    <t>[[49 71]
- [107 641]]</t>
-  </si>
-  <si>
-    <t>0: 0.73
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.78
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.76
-1: 0.78</t>
-  </si>
-  <si>
-    <t>[[310 88]
- [112 358]]</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.75</t>
-  </si>
-  <si>
-    <t>[[130 214]
- [81 443]]</t>
-  </si>
-  <si>
-    <t>{'n_neighbors': 2, 'weights': 'distance', 'algorithm': 'brute', 'leaf_size': 14, 'metric': 'cosine', 'n_jobs': -1}</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier E/I</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.85
-1: 0.26</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.40</t>
-  </si>
-  <si>
-    <t>[[171 29]
- [493 175]]</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier S/N</t>
-  </si>
-  <si>
-    <t>0: 0.15
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.72
-1: 0.32</t>
-  </si>
-  <si>
-    <t>0: 0.24
-1: 0.47</t>
-  </si>
-  <si>
-    <t>[[87 33]
- [509 239]]</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier T/F</t>
-  </si>
-  <si>
-    <t>0: 0.61
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.58
-1: 0.69</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.67</t>
-  </si>
-  <si>
-    <t>[[230 168]
- [145 325]]</t>
-  </si>
-  <si>
-    <t>KNeighboursClassifier J/P</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.63</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.65</t>
-  </si>
-  <si>
-    <t>[[143 201]
- [177 347]]</t>
-  </si>
-  <si>
-    <t>{'criterion': 'gini', 'max_depth': 15, 'min_samples_split': 9, 'min_samples_leaf': 4, 'max_features': None, 'class_weight': None, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier E/I</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.70</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.75</t>
-  </si>
-  <si>
-    <t>[[87 113]
- [201 467]]</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier S/N</t>
-  </si>
-  <si>
-    <t>0: 0.19
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[51 69]
- [213 535]]</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier T/F</t>
-  </si>
-  <si>
-    <t>0: 0.67
-1: 0.63</t>
-  </si>
-  <si>
-    <t>0: 0.63
-1: 0.66</t>
-  </si>
-  <si>
-    <t>[[265 133]
- [174 296]]</t>
-  </si>
-  <si>
-    <t>DecisionTreeClassifier J/P</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.62</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.65</t>
-  </si>
-  <si>
-    <t>0: 0.41
-1: 0.64</t>
-  </si>
-  <si>
-    <t>[[136 208]
- [182 342]]</t>
-  </si>
-  <si>
-    <t>0: 0.31
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.80</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.67
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.54
-1: 0.82</t>
-  </si>
-  <si>
-    <t>[[133 67]
- [157 511]]</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[72 48]
- [157 591]]</t>
-  </si>
-  <si>
-    <t>[[70 130]
- [81 587]]</t>
-  </si>
-  <si>
-    <t>0: 0.53
-1: 0.86</t>
-  </si>
-  <si>
-    <t>[[105 95]
- [92 576]]</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.95</t>
-  </si>
-  <si>
-    <t>0: 0.77
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.78</t>
-  </si>
-  <si>
-    <t>[[92 28]
- [251 497]]</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.50
-1: 0.83</t>
-  </si>
-  <si>
-    <t>[[113 87]
- [136 532]]</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.91</t>
-  </si>
-  <si>
-    <t>0: 0.44
-1: 0.86</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.88</t>
-  </si>
-  <si>
-    <t>[[53 67]
- [105 643]]</t>
-  </si>
-  <si>
-    <t>0: 0.26
-1: 0.85</t>
-  </si>
-  <si>
-    <t>0: 0.84
-1: 0.27</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.41</t>
-  </si>
-  <si>
-    <t>[[168 32]
- [488 180]]</t>
-  </si>
-  <si>
-    <t>0: 0.74
-1: 0.31</t>
-  </si>
-  <si>
-    <t>0: 0.25
-1: 0.46</t>
-  </si>
-  <si>
-    <t>[[89 31]
- [514 234]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.47
-1: 0.66</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.72</t>
-  </si>
-  <si>
-    <t>[[94 106]
- [229 439]]</t>
-  </si>
-  <si>
-    <t>0: 0.16
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.69</t>
-  </si>
-  <si>
-    <t>0: 0.23
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[46 74]
- [233 515]]</t>
-  </si>
-  <si>
-    <t>0: 0.42
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.51
-1: 0.79</t>
-  </si>
-  <si>
-    <t>0: 0.31
-1: 0.93</t>
-  </si>
-  <si>
-    <t>0: 0.65
-1: 0.77</t>
-  </si>
-  <si>
-    <t>0: 0.24
-1: 0.94</t>
-  </si>
-  <si>
-    <t>[[129 71]
- [156 512]]</t>
-  </si>
-  <si>
-    <t>0: 0.29
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.57
-1: 0.77</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.84</t>
-  </si>
-  <si>
-    <t>[[69 51]
- [170 578]]</t>
-  </si>
-  <si>
-    <t>0: 0.45
-1: 0.81</t>
-  </si>
-  <si>
-    <t>0: 0.33
-1: 0.88</t>
-  </si>
-  <si>
-    <t>[[66 134]
- [81 587]]</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.30
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[29 91]
- [47 701]]</t>
-  </si>
-  <si>
-    <t>0: 0.61
-1: 0.82</t>
-  </si>
-  <si>
-    <t>0: 0.33
-1: 0.94</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.88</t>
-  </si>
-  <si>
-    <t>[[66 134]
- [43 625]]</t>
-  </si>
-  <si>
-    <t>0: 0.41
-1: 0.89</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.91</t>
-  </si>
-  <si>
-    <t>[[37 83]
- [54 694]]</t>
-  </si>
-  <si>
-    <t>0: 0.41
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.67
-1: 0.71</t>
-  </si>
-  <si>
-    <t>[[133 67]
- [191 477]]</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.90</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.90</t>
-  </si>
-  <si>
-    <t>[[42 78]
- [73 675]]</t>
-  </si>
-  <si>
-    <t>0: 0.88
-1: 0.24</t>
-  </si>
-  <si>
-    <t>0: 0.40
-1: 0.38</t>
-  </si>
-  <si>
-    <t>[[175 25]
- [508 160]]</t>
-  </si>
-  <si>
-    <t>0: 0.14
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.76
-1: 0.28</t>
-  </si>
-  <si>
-    <t>0: 0.24
-1: 0.42</t>
-  </si>
-  <si>
-    <t>[[91 29]
- [542 206]]</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.63</t>
-  </si>
-  <si>
-    <t>0: 0.36
-1: 0.71</t>
-  </si>
-  <si>
-    <t>[[98 102]
- [245 423]]</t>
-  </si>
-  <si>
-    <t>0: 0.15
-1: 0.87</t>
-  </si>
-  <si>
-    <t>0: 0.33
-1: 0.69</t>
-  </si>
-  <si>
-    <t>0: 0.21
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[40 80]
- [229 519]]</t>
-  </si>
-  <si>
-    <t>0: 0.39
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.68
-1: 0.68</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.77</t>
-  </si>
-  <si>
-    <t>[[136 64]
- [214 454]]</t>
-  </si>
-  <si>
-    <t>0: 0.27
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.60
-1: 0.74</t>
-  </si>
-  <si>
-    <t>0: 0.37
-1: 0.82</t>
-  </si>
-  <si>
-    <t>[[72 48]
- [197 551]]</t>
-  </si>
-  <si>
-    <t>0: 0.38
-1: 0.83</t>
-  </si>
-  <si>
-    <t>0: 0.49
-1: 0.76</t>
-  </si>
-  <si>
-    <t>0: 0.43
-1: 0.79</t>
-  </si>
-  <si>
-    <t>[[98 102]
- [160 508]]</t>
-  </si>
-  <si>
-    <t>0: 0.56
-1: 0.88</t>
-  </si>
-  <si>
-    <t>0: 0.12
-1: 0.98</t>
-  </si>
-  <si>
-    <t>[[15 105]
- [12 736]]</t>
-  </si>
-  <si>
-    <t>0: 0.46
-1: 0.86</t>
-  </si>
-  <si>
     <t>0: 0.51
 1: 0.83</t>
   </si>
@@ -952,10 +908,6 @@
  [48 700]]</t>
   </si>
   <si>
-    <t>0: 0.42
-1: 0.85</t>
-  </si>
-  <si>
     <t>0: 0.55
 1: 0.77</t>
   </si>
@@ -1032,42 +984,74 @@
  [133 615]]</t>
   </si>
   <si>
+    <t>0: 0.69
+1: 0.69</t>
+  </si>
+  <si>
+    <t>0: 0.50
+1: 0.77</t>
+  </si>
+  <si>
+    <t>[[137 63]
+ [206 462]]</t>
+  </si>
+  <si>
+    <t>0: 0.26
+1: 0.92</t>
+  </si>
+  <si>
+    <t>0: 0.57
+1: 0.74</t>
+  </si>
+  <si>
+    <t>0: 0.36
+1: 0.82</t>
+  </si>
+  <si>
+    <t>[[69 51]
+ [198 550]]</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.83</t>
+  </si>
+  <si>
+    <t>0: 0.48
+1: 0.76</t>
+  </si>
+  <si>
+    <t>0: 0.42
+1: 0.79</t>
+  </si>
+  <si>
+    <t>[[97 103]
+ [163 505]]</t>
+  </si>
+  <si>
+    <t>0: 0.55
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.13
+1: 0.98</t>
+  </si>
+  <si>
+    <t>0: 0.21
+1: 0.93</t>
+  </si>
+  <si>
+    <t>[[16 104]
+ [13 735]]</t>
+  </si>
+  <si>
     <t>0: 0.36
 1: 0.87</t>
   </si>
   <si>
-    <t>0: 0.70
-1: 0.63</t>
-  </si>
-  <si>
     <t>0: 0.47
 1: 0.73</t>
   </si>
   <si>
-    <t>[[140 60]
- [250 418]]</t>
-  </si>
-  <si>
-    <t>0: 0.25
-1: 0.92</t>
-  </si>
-  <si>
-    <t>0: 0.59
-1: 0.72</t>
-  </si>
-  <si>
-    <t>0: 0.35
-1: 0.81</t>
-  </si>
-  <si>
-    <t>[[71 49]
- [211 537]]</t>
-  </si>
-  <si>
-    <t>0: 0.34
-1: 0.86</t>
-  </si>
-  <si>
     <t>0: 0.65
 1: 0.63</t>
   </si>
@@ -1076,18 +1060,10 @@
 1: 0.73</t>
   </si>
   <si>
-    <t>[[129 71]
- [246 422]]</t>
-  </si>
-  <si>
     <t>0: 0.22
 1: 0.92</t>
   </si>
   <si>
-    <t>[[18 102]
- [25 723]]</t>
-  </si>
-  <si>
     <t>0: 0.31
 1: 0.95</t>
   </si>
@@ -1104,22 +1080,6 @@
  [416 252]]</t>
   </si>
   <si>
-    <t>0: 0.18
-1: 0.98</t>
-  </si>
-  <si>
-    <t>0: 0.95
-1: 0.32</t>
-  </si>
-  <si>
-    <t>0: 0.31
-1: 0.49</t>
-  </si>
-  <si>
-    <t>[[114 6]
- [505 243]]</t>
-  </si>
-  <si>
     <t>0: 0.68
 1: 0.64</t>
   </si>
@@ -1206,6 +1166,58 @@
   <si>
     <t>[[35 85]
  [157 591]]</t>
+  </si>
+  <si>
+    <t>0: 0.70
+1: 0.62</t>
+  </si>
+  <si>
+    <t>[[140 60]
+ [253 415]]</t>
+  </si>
+  <si>
+    <t>0: 0.61
+1: 0.72</t>
+  </si>
+  <si>
+    <t>0: 0.37
+1: 0.81</t>
+  </si>
+  <si>
+    <t>[[73 47]
+ [206 542]]</t>
+  </si>
+  <si>
+    <t>0: 0.35
+1: 0.86</t>
+  </si>
+  <si>
+    <t>[[130 70]
+ [245 423]]</t>
+  </si>
+  <si>
+    <t>0: 0.14
+1: 0.97</t>
+  </si>
+  <si>
+    <t>0: 0.21
+1: 0.92</t>
+  </si>
+  <si>
+    <t>[[17 103]
+ [23 725]]</t>
+  </si>
+  <si>
+    <t>0: 0.52
+1: 0.88</t>
+  </si>
+  <si>
+    <t>0: 0.14
+1: 0.98</t>
+  </si>
+  <si>
+    <t>[[17 103]
+ [16 732]]</t>
   </si>
 </sst>
 </file>
@@ -1705,25 +1717,25 @@
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" s="5">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -1732,25 +1744,25 @@
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="F3" s="5">
         <v>0.76</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -1758,30 +1770,30 @@
         <v>11</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5">
         <v>0.75</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1790,25 +1802,25 @@
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5">
         <v>0.65</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1830,25 +1842,25 @@
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7" s="7">
         <v>0.76</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1857,25 +1869,25 @@
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1883,30 +1895,30 @@
         <v>11</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F9" s="7">
         <v>0.76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1915,25 +1927,25 @@
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F10" s="7">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1955,25 +1967,25 @@
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F12" s="9">
         <v>0.78</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1982,25 +1994,25 @@
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9">
         <v>0.68</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2008,30 +2020,30 @@
         <v>11</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F14" s="9">
         <v>0.67</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2040,25 +2052,25 @@
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F15" s="9">
         <v>0.54</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2080,25 +2092,25 @@
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2107,25 +2119,25 @@
     </row>
     <row r="18" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F18" s="11">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -2133,30 +2145,30 @@
         <v>11</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="11">
         <v>0.77</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2165,25 +2177,25 @@
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F20" s="11">
         <v>0.66</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -2203,54 +2215,54 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F22" s="13">
         <v>0.4</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F23" s="13">
         <v>0.37</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -2258,57 +2270,57 @@
         <v>11</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F24" s="13">
         <v>0.64</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F25" s="13">
         <v>0.56000000000000005</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -2328,54 +2340,54 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15">
         <v>0.61</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15">
         <v>0.65</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2383,57 +2395,57 @@
         <v>11</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F29" s="15">
         <v>0.65</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F30" s="15">
         <v>0.55000000000000004</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2481,25 +2493,25 @@
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" s="5">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -2508,25 +2520,25 @@
     </row>
     <row r="3" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
         <v>0.76</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>39</v>
+        <v>174</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -2534,30 +2546,30 @@
         <v>11</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5">
         <v>0.75</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2566,25 +2578,25 @@
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5">
         <v>0.65</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2606,25 +2618,25 @@
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7" s="7">
         <v>0.76</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2633,25 +2645,25 @@
     </row>
     <row r="8" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -2659,30 +2671,30 @@
         <v>11</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F9" s="7">
         <v>0.76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -2691,25 +2703,25 @@
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F10" s="7">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -2731,25 +2743,25 @@
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F12" s="9">
         <v>0.61</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2758,25 +2770,25 @@
     </row>
     <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9">
         <v>0.87</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2784,30 +2796,30 @@
         <v>11</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F14" s="9">
         <v>0.67</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2816,25 +2828,25 @@
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F15" s="9">
         <v>0.54</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2856,25 +2868,25 @@
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11">
         <v>0.71</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2883,25 +2895,25 @@
     </row>
     <row r="18" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F18" s="11">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -2909,30 +2921,30 @@
         <v>11</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="11">
         <v>0.77</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2941,25 +2953,25 @@
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F20" s="11">
         <v>0.66</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -2979,54 +2991,54 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F22" s="13">
         <v>0.4</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F23" s="13">
         <v>0.38</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -3034,57 +3046,57 @@
         <v>11</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F24" s="13">
         <v>0.64</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F25" s="13">
         <v>0.56000000000000005</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -3104,54 +3116,54 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15">
         <v>0.64</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15">
         <v>0.68</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -3159,57 +3171,57 @@
         <v>11</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F29" s="15">
         <v>0.65</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F30" s="15">
         <v>0.55000000000000004</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -3257,25 +3269,25 @@
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" s="5">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -3284,25 +3296,25 @@
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
         <v>0.75</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -3310,30 +3322,30 @@
         <v>11</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5">
         <v>0.75</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -3342,25 +3354,25 @@
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5">
         <v>0.65</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -3382,25 +3394,25 @@
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7" s="7">
         <v>0.75</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -3409,25 +3421,25 @@
     </row>
     <row r="8" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7">
         <v>0.84</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -3435,30 +3447,30 @@
         <v>11</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F9" s="7">
         <v>0.76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -3467,25 +3479,25 @@
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F10" s="7">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -3507,25 +3519,25 @@
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F12" s="9">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -3534,25 +3546,25 @@
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9">
         <v>0.84</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -3560,30 +3572,30 @@
         <v>11</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F14" s="9">
         <v>0.67</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -3592,25 +3604,25 @@
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F15" s="9">
         <v>0.54</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -3632,25 +3644,25 @@
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11">
         <v>0.7</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -3659,25 +3671,25 @@
     </row>
     <row r="18" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F18" s="11">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -3685,30 +3697,30 @@
         <v>11</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="11">
         <v>0.77</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -3717,25 +3729,25 @@
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F20" s="11">
         <v>0.66</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -3755,54 +3767,54 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F22" s="13">
         <v>0.39</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F23" s="13">
         <v>0.34</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -3810,57 +3822,57 @@
         <v>11</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F24" s="13">
         <v>0.64</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F25" s="13">
         <v>0.56000000000000005</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -3880,54 +3892,54 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15">
         <v>0.6</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15">
         <v>0.64</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -3935,57 +3947,57 @@
         <v>11</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F29" s="15">
         <v>0.65</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F30" s="15">
         <v>0.55000000000000004</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -4031,54 +4043,54 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" s="5">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -4086,57 +4098,57 @@
         <v>11</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5">
         <v>0.75</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5">
         <v>0.65</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -4156,54 +4168,54 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7" s="7">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7">
         <v>0.87</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -4211,57 +4223,57 @@
         <v>11</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F9" s="7">
         <v>0.76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F10" s="7">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -4281,54 +4293,54 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>9</v>
+        <v>223</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F12" s="9">
         <v>0.75</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9">
         <v>0.85</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -4336,57 +4348,57 @@
         <v>11</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F14" s="9">
         <v>0.67</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F15" s="9">
         <v>0.54</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -4406,54 +4418,54 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11">
         <v>0.72</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F18" s="11">
         <v>0.86</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -4461,57 +4473,57 @@
         <v>11</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="11">
         <v>0.77</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F20" s="11">
         <v>0.66</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -4531,54 +4543,54 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F22" s="13">
         <v>0.62</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F23" s="13">
         <v>0.78</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -4586,57 +4598,57 @@
         <v>11</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F24" s="13">
         <v>0.64</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F25" s="13">
         <v>0.56000000000000005</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -4656,54 +4668,54 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15">
         <v>0.59</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15">
         <v>0.75</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -4711,57 +4723,57 @@
         <v>11</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F29" s="15">
         <v>0.65</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F30" s="15">
         <v>0.55000000000000004</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -4807,54 +4819,54 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="F2" s="5">
         <v>0.64</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -4862,57 +4874,57 @@
         <v>11</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5">
         <v>0.75</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5">
         <v>0.65</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -4932,54 +4944,54 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7" s="7">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7">
         <v>0.85</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -4987,57 +4999,57 @@
         <v>11</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="F9" s="7">
         <v>0.76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F10" s="7">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -5057,54 +5069,54 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F12" s="9">
         <v>0.51</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9">
-        <v>0.41</v>
+        <v>0.86</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -5112,57 +5124,57 @@
         <v>11</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F14" s="9">
         <v>0.67</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F15" s="9">
         <v>0.54</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -5182,54 +5194,54 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11">
         <v>0.65</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F18" s="11">
         <v>0.85</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -5237,57 +5249,57 @@
         <v>11</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="11">
         <v>0.77</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="E20" s="11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F20" s="11">
         <v>0.66</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -5307,54 +5319,54 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F22" s="13">
         <v>0.59</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F23" s="13">
         <v>0.76</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -5362,57 +5374,57 @@
         <v>11</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F24" s="13">
         <v>0.64</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F25" s="13">
         <v>0.56000000000000005</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -5432,54 +5444,54 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15">
         <v>0.56000000000000005</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15">
         <v>0.72</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -5487,57 +5499,57 @@
         <v>11</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F29" s="15">
         <v>0.65</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F30" s="15">
         <v>0.55000000000000004</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
